--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect/Modeler</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
+          <t>https://www.indeed.com/viewjob?jk=fcba0d5ccb7003c8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Data Architect/Modeler</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
+          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
+          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
+          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - Power BI</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Broadview Federal Credit Union</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Databricks Lakehouse, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddee7a1fd9164fde</t>
+          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aae9352fc29e45e</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=782f670b324716aa</t>
+          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Kafka, Snowflake, SQL Server, ETL, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a4b202ac924d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,102 +2211,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beef8ad4f571f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, dbt, MLOps, Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c09f5f61dc700</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>16.7</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>16.7</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>16.7</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>16.7</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>16</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kafka, Kafka Connect, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52aa342dcce6e0db</t>
+          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>15.3</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,40 +2981,4100 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>Sr Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Federal Reserve Bank of St. Louis</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sr. Consultant SW Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr. Eng., Eng Services</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Invesco</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Engineer - MTS/SMTS</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ETL Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Cloud Operations Engineer - Boston</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>REsurety</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Trepp</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Clickhouse)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Highlands Ranch, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Unissant</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Abbott Park, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ahead</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II (Remote)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Kohl's</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Par Pacific Holdings</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Investments Technology</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Implementation Consultant</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4aae9352fc29e45e</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AutoSavvy</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Woods Cross, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Development Engineer II</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Intrado</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Longmont, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Thread Bank</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Power BI - Data Specialist</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Hammond, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Engineer IV- 4P/619</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4P Consulting Inc.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Engineer, Data Platform &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DEVELOPER L3(CONTRACT)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer | Digital Operations</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Beta Technologies</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>South Burlington, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sr. Application Security Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>WEX Inc.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee5e44d5f43b9ae9</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DEPARTMENT OF BUILDINGS</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Architect: Enterprise Data</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Mayer Brown LLP</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Foodsmart</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Specialist, Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Database Engineer 3 - Contingent (contract)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ETL Developer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Verinext</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Suwanee, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IT Intern - Data Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Weyerhaeuser</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DevSecOps Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ECS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Fairfax, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Snowflake Architect</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>DUO2 LLC</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf5dbb8dbe3266af</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer Analyst</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Quality Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Fisher Investments</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MySQL, MongoDB, Splunk, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4427659810ca0330</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Remote Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Astronaut Party Inc.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Enterprise Analytics BID</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deaconess Health System</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Evansville, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>COVERCRAFT INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Big Data Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Shannon &amp; Wilson Inc.</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Sightline Payments</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sr FedRAMP Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D.A. Davidson Companies</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer (Commercial)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>AutoZone</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer III</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Simplot Company</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer Prin</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Dayforce</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Tenex.Ai</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sr. Data Visualization Developer - Contractor</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Commonwealth of Massachusetts</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6aef2152855300a</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Java backend data engineer - Smithfield RI</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Photon</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Smithfield, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CardioOne</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CardioOne</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Loan Analytics &amp; AI Developer</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Trellance</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>HR -Data Scientist</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Senior Database Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, Kafka Connect, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52aa342dcce6e0db</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Skyworks Solutions</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>Irvine, CA, US USA</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G190" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e89891e4a957f47b</t>
         </is>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect/Modeler</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Ronin Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e10ec33698957c81</t>
+          <t>https://www.indeed.com/viewjob?jk=9c393b57d6602344</t>
         </is>
       </c>
     </row>
@@ -2918,35 +2918,35 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aae9352fc29e45e</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,94 +3751,94 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=4aae9352fc29e45e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Application Security Architect</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5e44d5f43b9ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,29 +4056,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Sr. Application Security Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5e44d5f43b9ae9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,94 +4136,94 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523330c74b38a27b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DUO2 LLC</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf5dbb8dbe3266af</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, MongoDB, Splunk, Jenkins, Jenkins, Git</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4427659810ca0330</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Quality Automation Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, MongoDB, Splunk, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,137 +4556,137 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=4427659810ca0330</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DUO2 LLC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bf5dbb8dbe3266af</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aef2152855300a</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aef2152855300a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,34 +6926,34 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b44f024bbd36d11</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, Kafka, Kafka Connect, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52aa342dcce6e0db</t>
+          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,15 +7066,155 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Loan Analytics &amp; AI Developer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Trellance</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>HR -Data Scientist</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Senior Database Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, Kafka Connect, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52aa342dcce6e0db</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Skyworks Solutions</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
+      <c r="G194" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e89891e4a957f47b</t>
         </is>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,12 +2568,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Databricks Data Architect - Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>BluEnt</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
+          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
+          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,52 +2936,52 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Federal Reserve Bank of St. Louis</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
         </is>
       </c>
     </row>
@@ -3128,25 +3128,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Back-End Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Spectrio LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdc93d3e13ebdd0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,19 +3366,19 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III – Cloud Platform Engineering - Python / AWS</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Scala, NoSQL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb199efc831c0dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=cf7e6921496659c0</t>
         </is>
       </c>
     </row>
@@ -3513,25 +3513,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aae9352fc29e45e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Azure Databricks Data Architect / Engineer (Public Sector)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Witriol Consulting</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=887e1abe8d5989a7</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Implementation Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=4aae9352fc29e45e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,94 +3856,94 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Application Security Architect</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5e44d5f43b9ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,29 +4161,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Sr. Application Security Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5e44d5f43b9ae9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,59 +4276,59 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, MongoDB, Splunk, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4427659810ca0330</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DUO2 LLC</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf5dbb8dbe3266af</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>DUO2 LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=bf5dbb8dbe3266af</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Application Security Analyst</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,137 +4731,137 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d58f2c1ddb77b874</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Automation Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>Fisher Investments</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, MongoDB, Splunk, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=4427659810ca0330</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aef2152855300a</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=c6aef2152855300a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Splunk, CI/CD, Azure DevOps, Docker</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f589c151e81c3302</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CardioOne</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,24 +7146,24 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Kraken</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Kafka, Kafka Connect, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52aa342dcce6e0db</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,15 +7206,225 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>CardioOne</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Senior Database Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, Kafka Connect, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52aa342dcce6e0db</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Skyworks Solutions</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e89891e4a957f47b</t>
         </is>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ronin Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c393b57d6602344</t>
+          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
+          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
+          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
+          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
+          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
+          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
+          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
+          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
+          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
+          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
+          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
+          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
+          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
+          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
+          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
+          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
+          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
+          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
+          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
+          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
+          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
+          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
+          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
+          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
+          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
+          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
+          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
+          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
+          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,42 +2351,42 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
+          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
         </is>
       </c>
     </row>
@@ -2568,12 +2568,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Databricks Data Architect - Consultant</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BluEnt</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c12fb6e67e8bda7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
+          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Graph DBA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
+          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,52 +2936,52 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af192f5dcbf84698</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Back-End Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Spectrio LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdc93d3e13ebdd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf7e6921496659c0</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Azure Databricks Data Architect / Engineer (Public Sector)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Witriol Consulting</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=887e1abe8d5989a7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Azure Databricks Data Architect / Engineer (Public Sector)</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Witriol Consulting</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, Power BI, CI/CD, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887e1abe8d5989a7</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Implementation Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Azure, Oracle, SQL Server, Data Modeling, ETL, Talend</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aae9352fc29e45e</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,94 +3856,94 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,67 +4136,67 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr. Application Security Architect</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5e44d5f43b9ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4227,46 +4227,46 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,59 +4276,59 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced77385e81a71b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DUO2 LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf5dbb8dbe3266af</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Application Security Analyst</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,137 +4731,137 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58f2c1ddb77b874</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fisher Investments</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, MongoDB, Splunk, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4427659810ca0330</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aef2152855300a</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CardioOne</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,322 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>CardioOne</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Senior Database Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Kraken</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AWS, Kafka, Kafka Connect, PostgreSQL, MongoDB, Cassandra, NoSQL, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52aa342dcce6e0db</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Skyworks Solutions</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLflow, CI/CD, Docker, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e89891e4a957f47b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
@@ -3268,17 +3268,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3828,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
@@ -4703,17 +4703,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5053,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,42 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>CardioOne</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>CO, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34653b24bff70a46</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,69 +3181,69 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7d736f0a5c3255</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3828,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
@@ -4143,17 +4143,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Database Engineer 3 - Contingent (contract)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
@@ -4703,17 +4703,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
@@ -6978,17 +6978,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2638,12 +2638,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,77 +2656,77 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23517bc36e765c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e736022550c4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b0320ba5b0219b</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Credit Risk (Hybrid) - New York, NY</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e782dc41b4055e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15f03a1274f889c</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Sr. Consultant SW Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b5a8aa7c2f7cd5</t>
+          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0522d81a23e6425</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Graph DBA</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fa9278e203e8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,102 +3296,102 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Azure Databricks Data Architect / Engineer (Public Sector)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Witriol Consulting</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=887e1abe8d5989a7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,137 +3541,137 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Azure Databricks Data Architect / Engineer (Public Sector)</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Witriol Consulting</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, Power BI, CI/CD, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887e1abe8d5989a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,67 +3751,67 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Platform Engineer | Digital Operations</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Beta Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,137 +3821,137 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e9557f408354fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Database Engineer 3 - Contingent (contract)</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,19 +4206,19 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b28c0b653e1b4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,102 +4311,102 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254d2582994d51f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,67 +4521,67 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,94 +4626,94 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Senior Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>Verra Mobility</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=452170f7558c869a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AvalonBay Communities</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, API Gateway, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d4406c73c381128</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6795,286 +6795,6 @@
         </is>
       </c>
       <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Commonwealth of Massachusetts</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Loan Analytics &amp; AI Developer</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Trellance</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Renton, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,12 +2568,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Senior Back End JS Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2582,46 +2582,46 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Consultant SW Engineer</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f337cce3b659c83d</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Avtech Solutions INC.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Azure Databricks Data Architect / Engineer (Public Sector)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Witriol Consulting</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, Power BI, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887e1abe8d5989a7</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
@@ -3548,12 +3548,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, DataOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741939e568ff083b</t>
+          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
         </is>
       </c>
     </row>
@@ -4073,17 +4073,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da1fa1569c709a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Cloud Network Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Verra Mobility</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=452170f7558c869a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AvalonBay Communities</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d4406c73c381128</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6725,76 +6725,6 @@
         </is>
       </c>
       <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Loan Analytics &amp; AI Developer</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Trellance</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Renton, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G180"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Back End JS Developer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Senior Back End JS Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,46 +2617,46 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,42 +2936,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,59 +2981,59 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Avtech Solutions INC.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Avtech Solutions INC.</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,59 +3576,59 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,49 +3821,49 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3877,38 +3877,38 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>COVERCRAFT INDUSTRIES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,94 +4346,94 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,42 +6691,182 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Loan Analytics &amp; AI Developer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Trellance</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>HR -Data Scientist</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Renton, WA, US USA</t>
         </is>
       </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
         <is>
           <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Sr. Data Visualization Developer - Contractor</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Commonwealth of Massachusetts</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Backend New</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CaseGuard</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>United Vein &amp; Vascular Centers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a9e3b0a9c943d41</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
+          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
+          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
+          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
+          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
+          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
+          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
+          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
+          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
+          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
+          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
+          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
+          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
+          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
+          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
+          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
+          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
+          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
+          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
+          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
+          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
+          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
+          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
+          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
+          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
+          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Back End JS Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,29 +2621,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Senior Back End JS Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2652,46 +2652,46 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,104 +3006,104 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Avtech Solutions INC.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Avtech Solutions INC.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a00da07441b7a67f</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Forward-Deployed Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
         </is>
       </c>
     </row>
@@ -3611,102 +3611,102 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,137 +3891,137 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a18554fdc47f587</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>QA Engineer / Automation Tester</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>COVERCRAFT INDUSTRIES</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5dc2c7f7fff79d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,129 +4451,129 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e17559f247cbc51a</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb676fb8407e921</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer – Backend New</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Java backend data engineer - Smithfield RI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend New</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,17 +6856,227 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Loan Analytics &amp; AI Developer</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Trellance</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>HR -Data Scientist</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sr. Data Visualization Developer - Contractor</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Commonwealth of Massachusetts</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>United Vein &amp; Vascular Centers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a9e3b0a9c943d41</t>
+          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
+          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
+          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
+          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
+          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
+          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
+          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
+          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
+          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
+          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
+          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
+          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
+          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
+          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
+          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
+          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
+          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
+          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
+          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
+          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
+          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
+          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
+          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
+          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
+          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
+          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
+          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
+          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
+          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
+          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
+          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
+          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Senior Back End JS Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Step Functions, RDS, Databricks, Medallion Architecture, GCP, Spark, Scala</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,147 +2631,147 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dccf18841adf6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Back End JS Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,94 +2841,94 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,42 +3006,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Avtech Solutions INC.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=793bcf53c033205f</t>
+          <t>https://www.indeed.com/viewjob?jk=c174e4a43011a2c9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Avtech Solutions INC.</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Cutsforth</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=8250b1164fbcace2</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2ca368a02b432d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>k1x</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
         </is>
       </c>
     </row>
@@ -4038,52 +4038,52 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer (On-Site Dallas)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>QA Engineer / Automation Tester</t>
+          <t>DevSecOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
+          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>QA Engineer / Automation Tester</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,29 +4336,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,69 +4546,69 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb676fb8407e921</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend New</t>
+          <t>Business Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
+          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Java backend data engineer - Smithfield RI</t>
+          <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, Snowflake, Oracle, Data Modeling, Star Schema, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d795ea45cb03ea9</t>
+          <t>https://www.indeed.com/viewjob?jk=cbb676fb8407e921</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Engineer – Backend New</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,7 +7076,42 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcba0d5ccb7003c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b61d40c84be0641c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fcba0d5ccb7003c8</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
+          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
+          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
+          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
+          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
+          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
+          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
+          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
+          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
+          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
+          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
+          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
+          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
+          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
+          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
+          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
+          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
+          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
+          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
+          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
+          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
+          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
+          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
+          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
+          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Back End JS Developer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Senior Back End JS Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,46 +2617,46 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, ETL, ELT</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1eb66e038f22b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Avtech Solutions INC.</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=c174e4a43011a2c9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c174e4a43011a2c9</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Cutsforth</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=8250b1164fbcace2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cutsforth</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250b1164fbcace2</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,59 +3296,59 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Forward-Deployed Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Forward-Deployed Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,54 +3681,54 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f81856c387866b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>k1x</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>k1x</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,42 +3986,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Suwanee, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer (On-Site Dallas)</t>
+          <t>QA Engineer / Automation Tester</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba872060c9bb68b6</t>
+          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DevSecOps Cloud Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, IAM, RDS, Azure, PostgreSQL, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96f58672f1d141ce</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>QA Engineer / Automation Tester</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,77 +4441,77 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,94 +4521,94 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,29 +4721,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Senior Software Engineer – Backend New</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer III</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6591940ddbd8809</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb676fb8407e921</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend New</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HR -Data Scientist</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>HR -Data Scientist</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,217 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -573,35 +573,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
+          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
+          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
+          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
+          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
+          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
+          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
+          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
+          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
+          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
+          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
+          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
+          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
+          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
+          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
+          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
+          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
+          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
+          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
+          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
+          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
+          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
+          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
+          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
+          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Back End JS Developer</t>
+          <t>Senior Data Engineer - SDE 26-04140</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,29 +2621,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Senior Back End JS Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2652,81 +2652,81 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Eng., Eng Services</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d1f24bbcec7861</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,69 +3006,69 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be868335e3ef6e98</t>
+          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior Cloud Operations Engineer - Boston</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c174e4a43011a2c9</t>
+          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=c174e4a43011a2c9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cutsforth</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250b1164fbcace2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Cutsforth</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=8250b1164fbcace2</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,59 +3296,59 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Data Engineer, Investments Technology</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Forward-Deployed Engineer</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Forward-Deployed Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>k1x</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>k1x</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,59 +3986,59 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4052,38 +4052,38 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Verinext</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Suwanee, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63d02d8862b8e251</t>
+          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IT Intern - Data Engineer</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6189d252c6c4d09f</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>QA Engineer / Automation Tester</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>QA Engineer / Automation Tester</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>Enterprise Analytics BID</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Deaconess Health System</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Evansville, IN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,42 +4441,42 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend New</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Engineer – Backend New</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009bef0a6c8cccee</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Steampunk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Hadoop, Hive, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12cc73e885e46940</t>
+          <t>https://www.indeed.com/viewjob?jk=fcba0d5ccb7003c8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61d40c84be0641c</t>
+          <t>https://www.indeed.com/viewjob?jk=c76e322a4d3ade18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Steampunk</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcba0d5ccb7003c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5e762c929a195ba8</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Back End JS Developer</t>
+          <t>Master Data Management (MDM) Consultant – Profisee Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Excelque</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b37c8ee4ee7bf02</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Senior Back End JS Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,81 +2687,81 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Eng., Eng Services</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,24 +2901,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f602056d9e789b25</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud Operations Engineer - Boston</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29974d87917cb0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c174e4a43011a2c9</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,42 +3216,42 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cutsforth</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250b1164fbcace2</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Forward-Deployed Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Investments Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24313a2ecfaf34</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,42 +3531,42 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Forward-Deployed Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,94 +3611,94 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Engineer, Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>k1x</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942e6a2e8d11f901</t>
+          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>k1x</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,42 +3986,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4052,38 +4052,38 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>QA Engineer / Automation Tester</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c0a369d519a555</t>
+          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>QA Engineer / Automation Tester</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Remote Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>Astronaut Party Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Enterprise Analytics BID</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deaconess Health System</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Evansville, IN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,112 +4371,112 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e89ffe2f4311bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Senior Systems Engineer (Commercial)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr. Software Engineer (Full-stack)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>UMB Financial Corporation</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Senior Software Engineer – Backend New</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend New</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,77 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Loan Analytics &amp; AI Developer</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Trellance</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>HR -Data Scientist</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Renton, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>RDS, Spark, ETL, dbt, Power BI, Tableau, MLflow, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7513f3b5f73b8498</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,77 +531,77 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76e322a4d3ade18</t>
+          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Ronin Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, EMR, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e762c929a195ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c393b57d6602344</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
+          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
+          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
+          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
+          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
+          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
+          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
+          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
+          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
+          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
+          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
+          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
+          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
+          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
+          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
+          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
+          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
+          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
+          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
+          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
+          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
+          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
+          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
+          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
+          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
+          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
+          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
+          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
+          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
+          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
+          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Master Data Management (MDM) Consultant – Profisee Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Excelque</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
+          <t>https://www.indeed.com/viewjob?jk=9b37c8ee4ee7bf02</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98bfdf8c981815d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b278bfb38191e0</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f397f88e84805b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - SDE 26-04140</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Medallion Architecture, Cloud Storage, Spark, PySpark</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b89ceef5f047ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Consultant – Profisee Platform</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Excelque</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b37c8ee4ee7bf02</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Back End JS Developer</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4297081d7551674e</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer (AWS/Azure/.Net/React/Angular/SQL)</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4f95bd6e7ce591</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,102 +2946,102 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7421e24a70553f85</t>
+          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Back End Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3212,38 +3212,38 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4db1e66cf2c5955</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Abbott Park, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04cba60ae1e318b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11754d25d1def69</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Forward-Deployed Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432bf674bdc9d04a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Forward-Deployed Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,77 +3461,77 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
+          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Thread Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5e7c5142ccaf15</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Remote Full-Stack Software Engineer</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Astronaut Party Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53661df7aef299c</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data/AI Engineering</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcaed35eb6ac63b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer (Commercial)</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Google Cloud Platform, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3623a3bc10b68</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
@@ -4808,17 +4808,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend New</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,17 +4896,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
@@ -6768,17 +6768,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Senior Software Engineer – Backend New</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,52 +6786,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Loan Analytics &amp; AI Developer</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Trellance</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-17.xlsx
+++ b/results/job_matches_2026-04-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS ARCHITECT - ECOMMERCE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Storage Asset Management</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>York, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
+          <t>https://www.indeed.com/viewjob?jk=f29e7767b416ec2c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ronin Consulting</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, NoSQL, ETL</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c393b57d6602344</t>
+          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>Data Engineer II-Promo Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
+          <t>^Application Support Engineer - 6249380</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
+          <t>https://www.indeed.com/viewjob?jk=83a4a649d48f54d4</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b193c2a47deffbb4</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd242c3c990deedb</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
+          <t>https://www.indeed.com/viewjob?jk=2561537e97c7c5cc</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
+          <t>https://www.indeed.com/viewjob?jk=099664cb507d0c0a</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfdfb8b9517134b</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f28818e6fa8ba413</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
+          <t>https://www.indeed.com/viewjob?jk=f0fd24a8ee2a5ec5</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bba9ac00cd1ce</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
+          <t>https://www.indeed.com/viewjob?jk=34862f84a678ce83</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
+          <t>https://www.indeed.com/viewjob?jk=3130f3e23789e011</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
+          <t>https://www.indeed.com/viewjob?jk=64424cac4b58fa19</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
+          <t>https://www.indeed.com/viewjob?jk=4930cd0acf0b7991</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
+          <t>https://www.indeed.com/viewjob?jk=a83dbc301b0d7150</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
+          <t>https://www.indeed.com/viewjob?jk=05981219368ec629</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c3559d4f159180</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=e927085fa2eb4729</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f19cfd985c6823aa</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
+          <t>https://www.indeed.com/viewjob?jk=42ccb73efd7f4fb0</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6304329fcd190e4</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
+          <t>https://www.indeed.com/viewjob?jk=b88b3a1c46a0fd45</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
+          <t>https://www.indeed.com/viewjob?jk=7eecef4c98476a7b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=40b52d0979b93968</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
+          <t>https://www.indeed.com/viewjob?jk=618efb317af5a303</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9d2a9153fe1fb6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86b6ce66e7fb28</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
+          <t>https://www.indeed.com/viewjob?jk=bdec13b195e879b6</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
+          <t>https://www.indeed.com/viewjob?jk=02d70d00000b8731</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
+          <t>https://www.indeed.com/viewjob?jk=66097a98a60fecbe</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0c1dcebe9c0298</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
+          <t>https://www.indeed.com/viewjob?jk=d726dca00cf5b3e0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb13165c5abb1</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
+          <t>https://www.indeed.com/viewjob?jk=f4877a578bc66931</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
+          <t>https://www.indeed.com/viewjob?jk=88418b5fe388512c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
+          <t>https://www.indeed.com/viewjob?jk=7481bdffbb97eb73</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=929dcdbe4c858c35</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
+          <t>https://www.indeed.com/viewjob?jk=04f7c098b8a7743e</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
+          <t>https://www.indeed.com/viewjob?jk=f09d83927ed81dcc</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
+          <t>https://www.indeed.com/viewjob?jk=87401a9ff10409ff</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=58db78c5bdf8b079</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=5e02c9b5d880d81d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
+          <t>https://www.indeed.com/viewjob?jk=df633814c9ca3e9e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
+          <t>https://www.indeed.com/viewjob?jk=c01fc425f02fff47</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5503c066b493ee0d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
+          <t>https://www.indeed.com/viewjob?jk=5967dff8ec7b114e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
+          <t>https://www.indeed.com/viewjob?jk=90584a02b9eee7f0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e96b3cedf77af9</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e46ce9c718010729</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdef157f015be34</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d90b7fa64c3d5ad</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,94 +2386,94 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ff7d0277b860e4be</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=277a451c099ebe1f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Deloitte Cyber Fullstack Senior Engineer/Senior Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
+          <t>https://www.indeed.com/viewjob?jk=130adb1ff3028dfc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Consultant – Profisee Platform</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Excelque</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,112 +2491,112 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b37c8ee4ee7bf02</t>
+          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Healthcare Interoperability)</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Verisma Systems Inc</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (Healthcare Interoperability)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Verisma Systems Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=a4adb393c0c5518d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Reliability Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Range Resources</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3188795e6538ca</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Range Resources</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=904977d520bdf5b0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - MTS/SMTS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer - MTS/SMTS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,42 +2866,42 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e86fac5a0813d91</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b4abca7667aec0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,42 +2971,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=941a8e269aca7287</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Back End Developer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdec629f0e3a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,24 +3286,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=27afa513de4d43c3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Forward-Deployed Engineer</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb64897e01ace612</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c121bf83d8e9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Power BI - Data Specialist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Thread Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hammond, LA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Kafka, Snowflake, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5e7c5142ccaf15</t>
+          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=aabd22e742757776</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer IV- 4P/619</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Power BI - Data Specialist</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hammond, LA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d77fd7ee06f384</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer IV- 4P/619</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Databricks Lakehouse, SQL Server, NoSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221bb6ab9cf8567d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Engineer, Data Platform &amp; Analytics</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec3bf6ef8f52ebe5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>k1x</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60943689647471d7</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,59 +3961,59 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior QA Automation Engineer New</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd964a7f985c7f20</t>
+          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>QA Engineer / Automation Tester</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01628e06adc6c80b</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,59 +4311,59 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Shannon &amp; Wilson Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15860cd51098fe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Sightline Payments</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Software Engineer III - Cloud Platform</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Sr FedRAMP Cloud Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shannon &amp; Wilson Inc.</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcece50ae2a44664</t>
+          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sightline Payments</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, MongoDB, NoSQL, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=604026874aa33ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Platform</t>
+          <t>Loan Analytics &amp; AI Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eb066c0ccadcb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr FedRAMP Cloud Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Tenex.Ai</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, Kafka, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c15b25df8b30bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr. Software Engineer (Full-stack)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>UMB Financial Corporation</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67989aa6e10bd139</t>
+          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data/AI Engineering</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcaed35eb6ac63b</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full-stack)</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>UMB Financial Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tenex.Ai</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, Docker, Kubernetes, Python</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4cd9c33b66b366</t>
+          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Loan Analytics &amp; AI Developer</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, ETL, Power BI, Tableau, Git, Python, SQL</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8996432c624d690f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Data Visualization Developer - Contractor</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Commonwealth of Massachusetts</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
+          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ada4a1f952be76e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=684438207f8ff675</t>
+          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c40cb05f11805da</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e07d5bd891a6c606</t>
+          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07373fd77eeccd1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3afc239ea06678</t>
+          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28338e69874fdad</t>
+          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e23e09a24997fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accce0f90367422f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a08fd2e14ff42a8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d5d835351b673c4</t>
+          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=019be7426dbb6af3</t>
+          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a65ede39acae4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea481f2750a3f1bf</t>
+          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb62779c169762cc</t>
+          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fb5d0118bd0fd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047a23d0a8ed2af9</t>
+          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ee6b290959edeb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49992ac30c26bab2</t>
+          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b1328a5fa626df</t>
+          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ea08345f9dd4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fded9cc68810fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a5a97a4021261</t>
+          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40c97658e8e281a</t>
+          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72637c051a81f470</t>
+          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c5c5a1422fe669</t>
+          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40a7efde29bcd71</t>
+          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37f78e6b527bc2b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d7dfd9f367b18b</t>
+          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e563d4401305a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29848e5f6b75d02</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497d95335c73c3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc664a9805f80d8e</t>
+          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394bef6008406869</t>
+          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4bfb1de8243686</t>
+          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2678a7bb77dd0e</t>
+          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4aba292627f9e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be2716e1a7c741</t>
+          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47ecf763980925f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fe6f966400ef1</t>
+          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47695660103c206d</t>
+          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e78237abd38094</t>
+          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec91c1f54041347</t>
+          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc59033f2d3d9663</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cfdce7376d95c98</t>
+          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=401879be632ac2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6541e818d4fd25</t>
+          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
+          <t>Sr. Data Visualization Developer - Contractor</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Commonwealth of Massachusetts</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,182 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bf4aab0844e010</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1562d49355cffc</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d90683951a6c8ba3</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b422d68469a1f25b</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Deloitte Cyber Fullstack Engineer Consultant</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>S3, Azure, Google Cloud Platform, Scala, NoSQL, Azure DevOps, Maven, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=885e5e27f5930400</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – Backend New</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>CaseGuard</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dbcba31adbe291</t>
+          <t>https://www.indeed.com/viewjob?jk=8f667ff007768704</t>
         </is>
       </c>
     </row>
